--- a/AppData.xlsx
+++ b/AppData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\RSP\EclipseProjects\BrowserStackDemo\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AF13AA3-66D5-4E85-BCF2-B3219B92260D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D860C833-FC29-4FB5-99A1-BB20B9CFAE24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="810" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{93FCCD10-3C25-470C-8A06-54571C881F11}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="56">
   <si>
     <t>Menu_1</t>
   </si>
@@ -117,6 +117,93 @@
   </si>
   <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>Bouncing Balls</t>
+  </si>
+  <si>
+    <t>Cloning</t>
+  </si>
+  <si>
+    <t>Custom Evaluator</t>
+  </si>
+  <si>
+    <t>Default Layout Animations</t>
+  </si>
+  <si>
+    <t>Events</t>
+  </si>
+  <si>
+    <t>Hide-Show Animations</t>
+  </si>
+  <si>
+    <t>Layout Animations</t>
+  </si>
+  <si>
+    <t>Loading</t>
+  </si>
+  <si>
+    <t>Multiple Properties</t>
+  </si>
+  <si>
+    <t>Reversing</t>
+  </si>
+  <si>
+    <t>Seeking</t>
+  </si>
+  <si>
+    <t>View Flip</t>
+  </si>
+  <si>
+    <t>Accessibility → Accessibility Node Provider</t>
+  </si>
+  <si>
+    <t>VerificationParameter</t>
+  </si>
+  <si>
+    <t>Validate Screen Title</t>
+  </si>
+  <si>
+    <t>Views → Controls → 1. Light Theme</t>
+  </si>
+  <si>
+    <t>Enter text</t>
+  </si>
+  <si>
+    <t>Toggle checkbox</t>
+  </si>
+  <si>
+    <t>Select radio</t>
+  </si>
+  <si>
+    <t>Click button</t>
+  </si>
+  <si>
+    <t>Views → Date Widgets → 1. Dialog</t>
+  </si>
+  <si>
+    <t>Open dialog</t>
+  </si>
+  <si>
+    <t>Select date</t>
+  </si>
+  <si>
+    <t>Confirm selection</t>
+  </si>
+  <si>
+    <t>Views → Drag and Drop</t>
+  </si>
+  <si>
+    <t>Drag dot from one place to another</t>
+  </si>
+  <si>
+    <t>Views → Expandable Lists → 1. Custom Adapter</t>
+  </si>
+  <si>
+    <t>Expand list</t>
+  </si>
+  <si>
+    <t>Click child item</t>
   </si>
 </sst>
 </file>
@@ -488,7 +575,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF2CA48-E06C-411C-83A6-9F6CF1EE6D5F}">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.42578125" customWidth="1"/>
@@ -570,13 +657,19 @@
       <c r="A6" t="s">
         <v>7</v>
       </c>
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
       <c r="G6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="B7" t="s">
+        <v>28</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
@@ -584,7 +677,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
@@ -592,7 +688,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
@@ -600,7 +699,10 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>
@@ -608,7 +710,10 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
@@ -616,7 +721,10 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>7</v>
+      </c>
+      <c r="B12" t="s">
+        <v>33</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
@@ -624,7 +732,10 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>14</v>
+        <v>7</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
@@ -632,16 +743,10 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" t="s">
-        <v>21</v>
-      </c>
-      <c r="F14" t="s">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
@@ -649,10 +754,191 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="G17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="G18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="G20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>13</v>
+      </c>
+      <c r="G23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F25" t="s">
+        <v>21</v>
+      </c>
+      <c r="G25" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>16</v>
       </c>
-      <c r="G15" t="s">
-        <v>25</v>
+      <c r="G26" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>39</v>
+      </c>
+      <c r="D28" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>47</v>
+      </c>
+      <c r="D33" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D34" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>53</v>
+      </c>
+      <c r="D37" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D38" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
